--- a/etf_holdings/2026-08-27_00405A_full_holdings.xlsx
+++ b/etf_holdings/2026-08-27_00405A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-27 16:57:38</t>
+          <t>2026-08-27 17:14:32</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-08-27 16:57:38</t>
+          <t>2026-08-27 17:14:32</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-27 16:57:38</t>
+          <t>2026-08-27 17:14:32</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-08-27 16:57:38</t>
+          <t>2026-08-27 17:14:32</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-08-27 16:57:38</t>
+          <t>2026-08-27 17:14:32</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-08-27 16:57:38</t>
+          <t>2026-08-27 17:14:32</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-08-27 16:57:38</t>
+          <t>2026-08-27 17:14:32</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-08-27 16:57:38</t>
+          <t>2026-08-27 17:14:32</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-08-27 16:57:38</t>
+          <t>2026-08-27 17:14:32</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-08-27 16:57:38</t>
+          <t>2026-08-27 17:14:32</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-08-27 16:57:38</t>
+          <t>2026-08-27 17:14:32</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-08-27 16:57:38</t>
+          <t>2026-08-27 17:14:32</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-08-27 16:57:38</t>
+          <t>2026-08-27 17:14:32</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-08-27 16:57:38</t>
+          <t>2026-08-27 17:14:32</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-08-27 16:57:38</t>
+          <t>2026-08-27 17:14:32</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-08-27 16:57:39</t>
+          <t>2026-08-27 17:14:34</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-08-27 16:57:39</t>
+          <t>2026-08-27 17:14:34</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-08-27 16:57:39</t>
+          <t>2026-08-27 17:14:34</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-08-27 16:57:39</t>
+          <t>2026-08-27 17:14:34</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-08-27 16:57:39</t>
+          <t>2026-08-27 17:14:34</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-08-27 16:57:39</t>
+          <t>2026-08-27 17:14:34</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-08-27 16:57:39</t>
+          <t>2026-08-27 17:14:34</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-08-27 16:57:39</t>
+          <t>2026-08-27 17:14:34</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-08-27 16:57:39</t>
+          <t>2026-08-27 17:14:34</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-08-27 16:57:39</t>
+          <t>2026-08-27 17:14:34</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-08-27 16:57:39</t>
+          <t>2026-08-27 17:14:34</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-08-27 16:57:39</t>
+          <t>2026-08-27 17:14:34</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-08-27 16:57:39</t>
+          <t>2026-08-27 17:14:34</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-08-27 16:57:39</t>
+          <t>2026-08-27 17:14:34</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-08-27 16:57:39</t>
+          <t>2026-08-27 17:14:34</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-08-27 16:57:40</t>
+          <t>2026-08-27 17:14:35</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-08-27 16:57:40</t>
+          <t>2026-08-27 17:14:35</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-08-27 16:57:40</t>
+          <t>2026-08-27 17:14:35</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-08-27 16:57:40</t>
+          <t>2026-08-27 17:14:35</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-08-27 16:57:40</t>
+          <t>2026-08-27 17:14:35</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-08-27 16:57:40</t>
+          <t>2026-08-27 17:14:35</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-08-27 16:57:40</t>
+          <t>2026-08-27 17:14:35</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-08-27 16:57:40</t>
+          <t>2026-08-27 17:14:35</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-08-27 16:57:40</t>
+          <t>2026-08-27 17:14:35</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-08-27 16:57:40</t>
+          <t>2026-08-27 17:14:35</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-08-27 16:57:40</t>
+          <t>2026-08-27 17:14:35</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-08-27 16:57:40</t>
+          <t>2026-08-27 17:14:35</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-08-27 16:57:40</t>
+          <t>2026-08-27 17:14:35</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-08-27 16:57:40</t>
+          <t>2026-08-27 17:14:35</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-08-27 16:57:40</t>
+          <t>2026-08-27 17:14:35</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">

--- a/etf_holdings/2026-08-27_00405A_full_holdings.xlsx
+++ b/etf_holdings/2026-08-27_00405A_full_holdings.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M46"/>
+  <dimension ref="A1:M51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-27 17:14:32</t>
+          <t>2026-08-27 19:39:25</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -504,38 +504,38 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>3443創意</t>
+          <t>3017奇鋐</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>-3.35%5920</t>
+          <t>+5.86%3340</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>-3.35%</t>
+          <t>+5.86%</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>5920</v>
+        <v>3340</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>8.62%419,000</t>
+          <t>9.00%803,000</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>8.62%</t>
+          <t>9.00%</t>
         </is>
       </c>
       <c r="K2" t="n">
-        <v>419000</v>
+        <v>803000</v>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>-0.30%</t>
+          <t>+0.50%</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-08-27 17:14:32</t>
+          <t>2026-08-27 19:39:25</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -565,38 +565,38 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>3017奇鋐</t>
+          <t>3443創意</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>+5.86%3340</t>
+          <t>-3.35%5920</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>+5.86%</t>
+          <t>-3.35%</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>3340</v>
+        <v>5920</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>8.51%803,000</t>
+          <t>8.32%419,000</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>8.51%</t>
+          <t>8.32%</t>
         </is>
       </c>
       <c r="K3" t="n">
-        <v>803000</v>
+        <v>419000</v>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>+0.47%</t>
+          <t>-0.29%</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-27 17:14:32</t>
+          <t>2026-08-27 19:39:25</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -644,12 +644,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>8.21%427,000</t>
+          <t>8.09%427,000</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>8.21%</t>
+          <t>8.09%</t>
         </is>
       </c>
       <c r="K4" t="n">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-08-27 17:14:32</t>
+          <t>2026-08-27 19:39:25</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -705,12 +705,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>6.36%480,000</t>
+          <t>6.23%480,000</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>6.36%</t>
+          <t>6.23%</t>
         </is>
       </c>
       <c r="K5" t="n">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-08-27 17:14:32</t>
+          <t>2026-08-27 19:39:25</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -748,38 +748,38 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>3665貿聯-KY</t>
+          <t>3037欣興</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>+2.49%2055</t>
+          <t>+1.72%1180</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>+2.49%</t>
+          <t>+1.72%</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>2055</v>
+        <v>1180</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>6.16%915,000</t>
+          <t>6.22%1,570,000</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>6.16%</t>
+          <t>6.22%</t>
         </is>
       </c>
       <c r="K6" t="n">
-        <v>915000</v>
+        <v>1570000</v>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>+0.15%</t>
+          <t>+0.11%</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-08-27 17:14:32</t>
+          <t>2026-08-27 19:39:25</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -809,38 +809,38 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>3037欣興</t>
+          <t>6223旺矽</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>+1.72%1180</t>
+          <t>+0.99%5090</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>+1.72%</t>
+          <t>+0.99%</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>1180</v>
+        <v>5090</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>6.12%1,570,000</t>
+          <t>4.66%273,000</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>6.12%</t>
+          <t>4.66%</t>
         </is>
       </c>
       <c r="K7" t="n">
-        <v>1570000</v>
+        <v>273000</v>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>+0.10%</t>
+          <t>+0.05%</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-08-27 17:14:32</t>
+          <t>2026-08-27 19:39:25</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -870,38 +870,38 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>6223旺矽</t>
+          <t>3665貿聯-KY</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>+0.99%5090</t>
+          <t>+2.49%2055</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>+0.99%</t>
+          <t>+2.49%</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>5090</v>
+        <v>2055</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>4.62%273,000</t>
+          <t>4.59%665,000</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>4.62%</t>
+          <t>4.59%</t>
         </is>
       </c>
       <c r="K8" t="n">
-        <v>273000</v>
+        <v>665000</v>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>+0.05%</t>
+          <t>+0.11%</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-08-27 17:14:32</t>
+          <t>2026-08-27 19:39:25</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -949,12 +949,12 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>4.20%212,000</t>
+          <t>3.91%212,000</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>4.20%</t>
+          <t>3.91%</t>
         </is>
       </c>
       <c r="K9" t="n">
@@ -962,7 +962,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>-0.30%</t>
+          <t>-0.28%</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-08-27 17:14:32</t>
+          <t>2026-08-27 19:39:25</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1010,12 +1010,12 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>3.94%1,127,000</t>
+          <t>3.90%1,127,000</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>3.94%</t>
+          <t>3.90%</t>
         </is>
       </c>
       <c r="K10" t="n">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-08-27 17:14:32</t>
+          <t>2026-08-27 19:39:25</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1071,12 +1071,12 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>3.65%529,000</t>
+          <t>3.71%529,000</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>3.65%</t>
+          <t>3.71%</t>
         </is>
       </c>
       <c r="K11" t="n">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-08-27 17:14:32</t>
+          <t>2026-08-27 19:39:25</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1132,12 +1132,12 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>2.93%739,000</t>
+          <t>3.21%739,000</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>2.93%</t>
+          <t>3.21%</t>
         </is>
       </c>
       <c r="K12" t="n">
@@ -1145,7 +1145,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>+0.26%</t>
+          <t>+0.29%</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-08-27 17:14:32</t>
+          <t>2026-08-27 19:39:25</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1193,12 +1193,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>2.86%54,300</t>
+          <t>2.79%54,300</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>2.86%</t>
+          <t>2.79%</t>
         </is>
       </c>
       <c r="K13" t="n">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-08-27 17:14:32</t>
+          <t>2026-08-27 19:39:25</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1254,12 +1254,12 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>2.55%120,000</t>
+          <t>2.56%120,000</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>2.55%</t>
+          <t>2.56%</t>
         </is>
       </c>
       <c r="K14" t="n">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-08-27 17:14:32</t>
+          <t>2026-08-27 19:39:25</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1297,38 +1297,38 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>6510精測</t>
+          <t>6531愛普*</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>+4.58%2740</t>
+          <t>+0.11%917</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>+4.58%</t>
+          <t>+0.11%</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>2740</v>
+        <v>917</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>2.16%245,000</t>
+          <t>2.31%750,000</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>2.16%</t>
+          <t>2.31%</t>
         </is>
       </c>
       <c r="K15" t="n">
-        <v>245000</v>
+        <v>750000</v>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>+0.09%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-08-27 17:14:32</t>
+          <t>2026-08-27 19:39:25</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1358,38 +1358,38 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2059川湖</t>
+          <t>6510精測</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>0%14340</t>
+          <t>+4.58%2740</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>+4.58%</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>14340</v>
+        <v>2740</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>2.05%42,000</t>
+          <t>2.25%245,000</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>2.05%</t>
+          <t>2.25%</t>
         </is>
       </c>
       <c r="K16" t="n">
-        <v>42000</v>
+        <v>245000</v>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>+0.10%</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-08-27 17:14:34</t>
+          <t>2026-08-27 19:39:26</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1437,12 +1437,12 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>1.97%1,200,000</t>
+          <t>2.17%1,200,000</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>1.97%</t>
+          <t>2.17%</t>
         </is>
       </c>
       <c r="K17" t="n">
@@ -1450,7 +1450,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>+0.18%</t>
+          <t>+0.20%</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-08-27 17:14:34</t>
+          <t>2026-08-27 19:39:26</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1480,38 +1480,38 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>3081聯亞</t>
+          <t>6805富世達</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>+3.53%3370</t>
+          <t>+9.88%2225</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>+3.53%</t>
+          <t>+9.88%</t>
         </is>
       </c>
       <c r="H18" t="n">
-        <v>3370</v>
+        <v>2225</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>1.73%158,400</t>
+          <t>2.02%271,000</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>1.73%</t>
+          <t>2.02%</t>
         </is>
       </c>
       <c r="K18" t="n">
-        <v>158400</v>
+        <v>271000</v>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>+0.06%</t>
+          <t>+0.18%</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-08-27 17:14:34</t>
+          <t>2026-08-27 19:39:26</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1541,38 +1541,38 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>6274台燿</t>
+          <t>2059川湖</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>-5.56%1445</t>
+          <t>0%14340</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>-5.56%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="H19" t="n">
-        <v>1445</v>
+        <v>14340</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>1.57%306,000</t>
+          <t>2.02%42,000</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>1.57%</t>
+          <t>2.02%</t>
         </is>
       </c>
       <c r="K19" t="n">
-        <v>306000</v>
+        <v>42000</v>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>-0.09%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-08-27 17:14:34</t>
+          <t>2026-08-27 19:39:26</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1602,38 +1602,38 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>7734印能科技</t>
+          <t>3081聯亞</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>-7.42%2870</t>
+          <t>+3.53%3370</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>-7.42%</t>
+          <t>+3.53%</t>
         </is>
       </c>
       <c r="H20" t="n">
-        <v>2870</v>
+        <v>3370</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>1.56%150,000</t>
+          <t>1.79%158,400</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>1.56%</t>
+          <t>1.79%</t>
         </is>
       </c>
       <c r="K20" t="n">
-        <v>150000</v>
+        <v>158400</v>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>-0.13%</t>
+          <t>+0.06%</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-08-27 17:14:34</t>
+          <t>2026-08-27 19:39:26</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1663,38 +1663,38 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>2330台積電</t>
+          <t>6274台燿</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>-0.21%2410</t>
+          <t>-5.56%1445</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>-0.21%</t>
+          <t>-5.56%</t>
         </is>
       </c>
       <c r="H21" t="n">
-        <v>2410</v>
+        <v>1445</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>1.45%179,000</t>
+          <t>1.48%306,000</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>1.45%</t>
+          <t>1.48%</t>
         </is>
       </c>
       <c r="K21" t="n">
-        <v>179000</v>
+        <v>306000</v>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>-0.09%</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-08-27 17:14:34</t>
+          <t>2026-08-27 19:39:26</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1724,38 +1724,38 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>6805富世達</t>
+          <t>2330台積電</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>+9.88%2225</t>
+          <t>-0.21%2410</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>+9.88%</t>
+          <t>-0.21%</t>
         </is>
       </c>
       <c r="H22" t="n">
-        <v>2225</v>
+        <v>2410</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>1.37%201,000</t>
+          <t>1.45%179,000</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>1.37%</t>
+          <t>1.45%</t>
         </is>
       </c>
       <c r="K22" t="n">
-        <v>201000</v>
+        <v>179000</v>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>+0.12%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-08-27 17:14:34</t>
+          <t>2026-08-27 19:39:26</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1785,38 +1785,38 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>3131弘塑</t>
+          <t>7734印能科技</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>+0.2%2490</t>
+          <t>-7.42%2870</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>+0.2%</t>
+          <t>-7.42%</t>
         </is>
       </c>
       <c r="H23" t="n">
-        <v>2490</v>
+        <v>2870</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>1.35%162,000</t>
+          <t>1.44%150,000</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>1.35%</t>
+          <t>1.44%</t>
         </is>
       </c>
       <c r="K23" t="n">
-        <v>162000</v>
+        <v>150000</v>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.12%</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-08-27 17:14:34</t>
+          <t>2026-08-27 19:39:26</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1846,38 +1846,38 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>3450聯鈞</t>
+          <t>3131弘塑</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>+0.7%578</t>
+          <t>+0.2%2490</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>+0.7%</t>
+          <t>+0.2%</t>
         </is>
       </c>
       <c r="H24" t="n">
-        <v>578</v>
+        <v>2490</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>1.25%650,000</t>
+          <t>1.27%152,000</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>1.25%</t>
+          <t>1.27%</t>
         </is>
       </c>
       <c r="K24" t="n">
-        <v>650000</v>
+        <v>152000</v>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-08-27 17:14:34</t>
+          <t>2026-08-27 19:39:26</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1907,34 +1907,34 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>6669緯穎</t>
+          <t>3450聯鈞</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>+0.44%6815</t>
+          <t>+0.7%578</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>+0.44%</t>
+          <t>+0.7%</t>
         </is>
       </c>
       <c r="H25" t="n">
-        <v>6815</v>
+        <v>578</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>1.14%50,000</t>
+          <t>1.26%650,000</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>1.14%</t>
+          <t>1.26%</t>
         </is>
       </c>
       <c r="K25" t="n">
-        <v>50000</v>
+        <v>650000</v>
       </c>
       <c r="L25" t="inlineStr">
         <is>
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-08-27 17:14:34</t>
+          <t>2026-08-27 19:39:26</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1986,12 +1986,12 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>1.13%282,000</t>
+          <t>1.24%282,000</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>1.13%</t>
+          <t>1.24%</t>
         </is>
       </c>
       <c r="K26" t="n">
@@ -1999,7 +1999,7 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>+0.10%</t>
+          <t>+0.11%</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-08-27 17:14:34</t>
+          <t>2026-08-27 19:39:26</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2029,38 +2029,38 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>6531愛普*</t>
+          <t>6669緯穎</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>+0.11%917</t>
+          <t>+0.44%6815</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>+0.11%</t>
+          <t>+0.44%</t>
         </is>
       </c>
       <c r="H27" t="n">
-        <v>917</v>
+        <v>6815</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>0.92%300,000</t>
+          <t>1.14%50,000</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>0.92%</t>
+          <t>1.14%</t>
         </is>
       </c>
       <c r="K27" t="n">
-        <v>300000</v>
+        <v>50000</v>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-08-27 17:14:34</t>
+          <t>2026-08-27 19:39:26</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2090,38 +2090,38 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>6187萬潤</t>
+          <t>6278台表科</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>+10%1430</t>
+          <t>+3.26%206</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>+10%</t>
+          <t>+3.26%</t>
         </is>
       </c>
       <c r="H28" t="n">
-        <v>1430</v>
+        <v>206</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>0.86%198,000</t>
+          <t>0.97%1,400,000</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>0.86%</t>
+          <t>0.97%</t>
         </is>
       </c>
       <c r="K28" t="n">
-        <v>198000</v>
+        <v>1400000</v>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>+0.08%</t>
+          <t>+0.03%</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-08-27 17:14:34</t>
+          <t>2026-08-27 19:39:26</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2151,38 +2151,38 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>2308台達電</t>
+          <t>6187萬潤</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>+1.14%1770</t>
+          <t>+10%1430</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>+1.14%</t>
+          <t>+10%</t>
         </is>
       </c>
       <c r="H29" t="n">
-        <v>1770</v>
+        <v>1430</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>0.55%94,000</t>
+          <t>0.95%198,000</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>0.55%</t>
+          <t>0.95%</t>
         </is>
       </c>
       <c r="K29" t="n">
-        <v>94000</v>
+        <v>198000</v>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>+0.09%</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-08-27 17:14:34</t>
+          <t>2026-08-27 19:39:26</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2212,38 +2212,38 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>8210勤誠</t>
+          <t>2308台達電</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>-1.44%960</t>
+          <t>+1.14%1770</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>-1.44%</t>
+          <t>+1.14%</t>
         </is>
       </c>
       <c r="H30" t="n">
-        <v>960</v>
+        <v>1770</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>0.55%168,000</t>
+          <t>0.56%94,000</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>0.55%</t>
+          <t>0.56%</t>
         </is>
       </c>
       <c r="K30" t="n">
-        <v>168000</v>
+        <v>94000</v>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-08-27 17:14:34</t>
+          <t>2026-08-27 19:39:26</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2273,38 +2273,38 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>6831邁科</t>
+          <t>8210勤誠</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>+2.95%593</t>
+          <t>-1.44%960</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>+2.95%</t>
+          <t>-1.44%</t>
         </is>
       </c>
       <c r="H31" t="n">
-        <v>593</v>
+        <v>960</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>0.48%250,000</t>
+          <t>0.54%168,000</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>0.48%</t>
+          <t>0.54%</t>
         </is>
       </c>
       <c r="K31" t="n">
-        <v>250000</v>
+        <v>168000</v>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-08-27 17:14:35</t>
+          <t>2026-08-27 19:39:28</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2334,34 +2334,34 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>6515穎崴</t>
+          <t>6831邁科</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>+1.33%6105</t>
+          <t>+2.95%593</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>+1.33%</t>
+          <t>+2.95%</t>
         </is>
       </c>
       <c r="H32" t="n">
-        <v>6105</v>
+        <v>593</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>0.47%23,000</t>
+          <t>0.50%250,000</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>0.47%</t>
+          <t>0.50%</t>
         </is>
       </c>
       <c r="K32" t="n">
-        <v>23000</v>
+        <v>250000</v>
       </c>
       <c r="L32" t="inlineStr">
         <is>
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-08-27 17:14:35</t>
+          <t>2026-08-27 19:39:28</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2395,38 +2395,38 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>6488環球晶</t>
+          <t>6515穎崴</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>+0.95%958</t>
+          <t>+1.33%6105</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>+0.95%</t>
+          <t>+1.33%</t>
         </is>
       </c>
       <c r="H33" t="n">
-        <v>958</v>
+        <v>6105</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>0.35%110,000</t>
+          <t>0.47%23,000</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>0.35%</t>
+          <t>0.47%</t>
         </is>
       </c>
       <c r="K33" t="n">
-        <v>110000</v>
+        <v>23000</v>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-08-27 17:14:35</t>
+          <t>2026-08-27 19:39:28</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2456,34 +2456,34 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>6285啟碁</t>
+          <t>6488環球晶</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>+1.24%245</t>
+          <t>+0.95%958</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>+1.24%</t>
+          <t>+0.95%</t>
         </is>
       </c>
       <c r="H34" t="n">
-        <v>245</v>
+        <v>958</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>0.33%400,000</t>
+          <t>0.35%110,000</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>0.33%</t>
+          <t>0.35%</t>
         </is>
       </c>
       <c r="K34" t="n">
-        <v>400000</v>
+        <v>110000</v>
       </c>
       <c r="L34" t="inlineStr">
         <is>
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-08-27 17:14:35</t>
+          <t>2026-08-27 19:39:28</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2517,38 +2517,38 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>6526達發</t>
+          <t>6285啟碁</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>+2.52%610</t>
+          <t>+1.24%245</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>+2.52%</t>
+          <t>+1.24%</t>
         </is>
       </c>
       <c r="H35" t="n">
-        <v>610</v>
+        <v>245</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>0.29%146,000</t>
+          <t>0.33%400,000</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>0.29%</t>
+          <t>0.33%</t>
         </is>
       </c>
       <c r="K35" t="n">
-        <v>146000</v>
+        <v>400000</v>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-08-27 17:14:35</t>
+          <t>2026-08-27 19:39:28</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2578,34 +2578,34 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>4749新應材</t>
+          <t>6526達發</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>+4.5%789</t>
+          <t>+2.52%610</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>+4.5%</t>
+          <t>+2.52%</t>
         </is>
       </c>
       <c r="H36" t="n">
-        <v>789</v>
+        <v>610</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>0.24%95,000</t>
+          <t>0.30%146,000</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>0.24%</t>
+          <t>0.30%</t>
         </is>
       </c>
       <c r="K36" t="n">
-        <v>95000</v>
+        <v>146000</v>
       </c>
       <c r="L36" t="inlineStr">
         <is>
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-08-27 17:14:35</t>
+          <t>2026-08-27 19:39:28</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2639,38 +2639,38 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>5347世界</t>
+          <t>4749新應材</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>-0.66%151</t>
+          <t>+4.5%789</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>-0.66%</t>
+          <t>+4.5%</t>
         </is>
       </c>
       <c r="H37" t="n">
-        <v>151</v>
+        <v>789</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>0.11%211,000</t>
+          <t>0.25%95,000</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>0.11%</t>
+          <t>0.25%</t>
         </is>
       </c>
       <c r="K37" t="n">
-        <v>211000</v>
+        <v>95000</v>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-08-27 17:14:35</t>
+          <t>2026-08-27 19:39:28</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2700,38 +2700,38 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>4576大銀微系統</t>
+          <t>5347世界</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>+6.16%215.5</t>
+          <t>-0.66%151</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>+6.16%</t>
+          <t>-0.66%</t>
         </is>
       </c>
       <c r="H38" t="n">
-        <v>215.5</v>
+        <v>151</v>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>0.05%72,000</t>
+          <t>0.11%211,000</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>0.05%</t>
+          <t>0.11%</t>
         </is>
       </c>
       <c r="K38" t="n">
-        <v>72000</v>
+        <v>211000</v>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-08-27 17:14:35</t>
+          <t>2026-08-27 19:39:28</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2761,34 +2761,34 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>2449京元電子</t>
+          <t>4576大銀微系統</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>+1.43%247.5</t>
+          <t>+6.16%215.5</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>+1.43%</t>
+          <t>+6.16%</t>
         </is>
       </c>
       <c r="H39" t="n">
-        <v>247.5</v>
+        <v>215.5</v>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>0.03%42,650</t>
+          <t>0.05%72,000</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>0.03%</t>
+          <t>0.05%</t>
         </is>
       </c>
       <c r="K39" t="n">
-        <v>42650</v>
+        <v>72000</v>
       </c>
       <c r="L39" t="inlineStr">
         <is>
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-08-27 17:14:35</t>
+          <t>2026-08-27 19:39:28</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2822,38 +2822,38 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>3163波若威</t>
+          <t>2449京元電子</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>-0.13%776</t>
+          <t>+1.43%247.5</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>-0.13%</t>
+          <t>+1.43%</t>
         </is>
       </c>
       <c r="H40" t="n">
-        <v>776</v>
+        <v>247.5</v>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>0.03%13,300</t>
+          <t>0.04%42,650</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>0.03%</t>
+          <t>0.04%</t>
         </is>
       </c>
       <c r="K40" t="n">
-        <v>13300</v>
+        <v>42650</v>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-08-27 17:14:35</t>
+          <t>2026-08-27 19:39:28</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2883,25 +2883,25 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>2303聯電</t>
+          <t>3163波若威</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>-4.05%118.5</t>
+          <t>-0.13%776</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>-4.05%</t>
+          <t>-0.13%</t>
         </is>
       </c>
       <c r="H41" t="n">
-        <v>118.5</v>
+        <v>776</v>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>0.03%78,000</t>
+          <t>0.03%13,300</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -2910,7 +2910,7 @@
         </is>
       </c>
       <c r="K41" t="n">
-        <v>78000</v>
+        <v>13300</v>
       </c>
       <c r="L41" t="inlineStr">
         <is>
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-08-27 17:14:35</t>
+          <t>2026-08-27 19:39:28</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2944,38 +2944,38 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>3264欣銓</t>
+          <t>2303聯電</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>+0.92%219.5</t>
+          <t>-4.05%118.5</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>+0.92%</t>
+          <t>-4.05%</t>
         </is>
       </c>
       <c r="H42" t="n">
-        <v>219.5</v>
+        <v>118.5</v>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>0.02%34,000</t>
+          <t>0.03%78,000</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>0.02%</t>
+          <t>0.03%</t>
         </is>
       </c>
       <c r="K42" t="n">
-        <v>34000</v>
+        <v>78000</v>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-08-27 17:14:35</t>
+          <t>2026-08-27 19:39:28</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3005,34 +3005,34 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>8021尖點</t>
+          <t>3264欣銓</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>+0.96%422.5</t>
+          <t>+0.92%219.5</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>+0.96%</t>
+          <t>+0.92%</t>
         </is>
       </c>
       <c r="H43" t="n">
-        <v>422.5</v>
+        <v>219.5</v>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>0.01%10,000</t>
+          <t>0.03%34,000</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>0.01%</t>
+          <t>0.03%</t>
         </is>
       </c>
       <c r="K43" t="n">
-        <v>10000</v>
+        <v>34000</v>
       </c>
       <c r="L43" t="inlineStr">
         <is>
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-08-27 17:14:35</t>
+          <t>2026-08-27 19:39:28</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3066,25 +3066,25 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>3661世芯-KY</t>
+          <t>8021尖點</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>-2.27%3870</t>
+          <t>+0.96%422.5</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>-2.27%</t>
+          <t>+0.96%</t>
         </is>
       </c>
       <c r="H44" t="n">
-        <v>3870</v>
+        <v>422.5</v>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>0.01%1,000</t>
+          <t>0.01%10,000</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -3093,11 +3093,11 @@
         </is>
       </c>
       <c r="K44" t="n">
-        <v>1000</v>
+        <v>10000</v>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-08-27 17:14:35</t>
+          <t>2026-08-27 19:39:28</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3127,25 +3127,25 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>2395研華</t>
+          <t>3661世芯-KY</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>-1.89%675</t>
+          <t>-2.27%3870</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>-1.89%</t>
+          <t>-2.27%</t>
         </is>
       </c>
       <c r="H45" t="n">
-        <v>675</v>
+        <v>3870</v>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>0.01%5,000</t>
+          <t>0.01%1,000</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -3154,7 +3154,7 @@
         </is>
       </c>
       <c r="K45" t="n">
-        <v>5000</v>
+        <v>1000</v>
       </c>
       <c r="L45" t="inlineStr">
         <is>
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-08-27 17:14:35</t>
+          <t>2026-08-27 19:39:28</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3188,41 +3188,346 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
+          <t>2395研華</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>-1.89%675</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>-1.89%</t>
+        </is>
+      </c>
+      <c r="H46" t="n">
+        <v>675</v>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>0.01%5,000</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>0.01%</t>
+        </is>
+      </c>
+      <c r="K46" t="n">
+        <v>5000</v>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>-0.00%</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>登入查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>00405A</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>2026-08-27 19:39:29</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>https://www.etfinfo.tw/etf/00405A/holdings</t>
+        </is>
+      </c>
+      <c r="D47" t="n">
+        <v>4</v>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
           <t>3711日月光投控</t>
         </is>
       </c>
-      <c r="F46" t="inlineStr">
+      <c r="F47" t="inlineStr">
         <is>
           <t>+2.2%605</t>
         </is>
       </c>
-      <c r="G46" t="inlineStr">
+      <c r="G47" t="inlineStr">
         <is>
           <t>+2.2%</t>
         </is>
       </c>
-      <c r="H46" t="n">
+      <c r="H47" t="n">
         <v>605</v>
       </c>
-      <c r="I46" t="inlineStr">
+      <c r="I47" t="inlineStr">
         <is>
           <t>&lt;0.01%3,000</t>
         </is>
       </c>
-      <c r="J46" t="inlineStr">
+      <c r="J47" t="inlineStr">
         <is>
           <t>&lt;0.01%</t>
         </is>
       </c>
-      <c r="K46" t="n">
+      <c r="K47" t="n">
         <v>3000</v>
       </c>
-      <c r="L46" t="inlineStr">
+      <c r="L47" t="inlineStr">
         <is>
           <t>+0.00%</t>
         </is>
       </c>
-      <c r="M46" t="inlineStr">
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>登入查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>00405A</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>2026-08-27 19:39:29</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>https://www.etfinfo.tw/etf/00405A/holdings</t>
+        </is>
+      </c>
+      <c r="D48" t="n">
+        <v>4</v>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>3533嘉澤</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>0%1625</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="H48" t="n">
+        <v>1625</v>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>&lt;0.01%1,000</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>&lt;0.01%</t>
+        </is>
+      </c>
+      <c r="K48" t="n">
+        <v>1000</v>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>+0.00%</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>登入查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>00405A</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>2026-08-27 19:39:29</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>https://www.etfinfo.tw/etf/00405A/holdings</t>
+        </is>
+      </c>
+      <c r="D49" t="n">
+        <v>4</v>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>1590亞德客-KY</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>+0.68%1480</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>+0.68%</t>
+        </is>
+      </c>
+      <c r="H49" t="n">
+        <v>1480</v>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>&lt;0.01%1,000</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>&lt;0.01%</t>
+        </is>
+      </c>
+      <c r="K49" t="n">
+        <v>1000</v>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>+0.00%</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>登入查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>00405A</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>2026-08-27 19:39:29</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>https://www.etfinfo.tw/etf/00405A/holdings</t>
+        </is>
+      </c>
+      <c r="D50" t="n">
+        <v>4</v>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>3491昇達科</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>+5.95%1425</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>+5.95%</t>
+        </is>
+      </c>
+      <c r="H50" t="n">
+        <v>1425</v>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>&lt;0.01%1,000</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>&lt;0.01%</t>
+        </is>
+      </c>
+      <c r="K50" t="n">
+        <v>1000</v>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>+0.00%</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>登入查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>00405A</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>2026-08-27 19:39:29</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>https://www.etfinfo.tw/etf/00405A/holdings</t>
+        </is>
+      </c>
+      <c r="D51" t="n">
+        <v>4</v>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>8028昇陽半導體</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>+0.81%248.5</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>+0.81%</t>
+        </is>
+      </c>
+      <c r="H51" t="n">
+        <v>248.5</v>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>&lt;0.01%1,000</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>&lt;0.01%</t>
+        </is>
+      </c>
+      <c r="K51" t="n">
+        <v>1000</v>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>+0.00%</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
         <is>
           <t>登入查看</t>
         </is>

--- a/etf_holdings/2026-08-27_00405A_full_holdings.xlsx
+++ b/etf_holdings/2026-08-27_00405A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-27 19:39:25</t>
+          <t>2026-08-27 22:49:49</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-08-27 19:39:25</t>
+          <t>2026-08-27 22:49:49</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-27 19:39:25</t>
+          <t>2026-08-27 22:49:49</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-08-27 19:39:25</t>
+          <t>2026-08-27 22:49:49</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-08-27 19:39:25</t>
+          <t>2026-08-27 22:49:49</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-08-27 19:39:25</t>
+          <t>2026-08-27 22:49:49</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-08-27 19:39:25</t>
+          <t>2026-08-27 22:49:49</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-08-27 19:39:25</t>
+          <t>2026-08-27 22:49:49</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-08-27 19:39:25</t>
+          <t>2026-08-27 22:49:49</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-08-27 19:39:25</t>
+          <t>2026-08-27 22:49:49</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-08-27 19:39:25</t>
+          <t>2026-08-27 22:49:49</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-08-27 19:39:25</t>
+          <t>2026-08-27 22:49:49</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-08-27 19:39:25</t>
+          <t>2026-08-27 22:49:49</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-08-27 19:39:25</t>
+          <t>2026-08-27 22:49:49</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-08-27 19:39:25</t>
+          <t>2026-08-27 22:49:49</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-08-27 19:39:26</t>
+          <t>2026-08-27 22:49:51</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-08-27 19:39:26</t>
+          <t>2026-08-27 22:49:51</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-08-27 19:39:26</t>
+          <t>2026-08-27 22:49:51</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-08-27 19:39:26</t>
+          <t>2026-08-27 22:49:51</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-08-27 19:39:26</t>
+          <t>2026-08-27 22:49:51</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-08-27 19:39:26</t>
+          <t>2026-08-27 22:49:51</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-08-27 19:39:26</t>
+          <t>2026-08-27 22:49:51</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-08-27 19:39:26</t>
+          <t>2026-08-27 22:49:51</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-08-27 19:39:26</t>
+          <t>2026-08-27 22:49:51</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-08-27 19:39:26</t>
+          <t>2026-08-27 22:49:51</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-08-27 19:39:26</t>
+          <t>2026-08-27 22:49:51</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-08-27 19:39:26</t>
+          <t>2026-08-27 22:49:51</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-08-27 19:39:26</t>
+          <t>2026-08-27 22:49:51</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-08-27 19:39:26</t>
+          <t>2026-08-27 22:49:51</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-08-27 19:39:26</t>
+          <t>2026-08-27 22:49:51</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-08-27 19:39:28</t>
+          <t>2026-08-27 22:49:52</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-08-27 19:39:28</t>
+          <t>2026-08-27 22:49:52</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-08-27 19:39:28</t>
+          <t>2026-08-27 22:49:52</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-08-27 19:39:28</t>
+          <t>2026-08-27 22:49:52</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-08-27 19:39:28</t>
+          <t>2026-08-27 22:49:52</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-08-27 19:39:28</t>
+          <t>2026-08-27 22:49:52</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-08-27 19:39:28</t>
+          <t>2026-08-27 22:49:52</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-08-27 19:39:28</t>
+          <t>2026-08-27 22:49:52</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-08-27 19:39:28</t>
+          <t>2026-08-27 22:49:52</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-08-27 19:39:28</t>
+          <t>2026-08-27 22:49:52</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-08-27 19:39:28</t>
+          <t>2026-08-27 22:49:52</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-08-27 19:39:28</t>
+          <t>2026-08-27 22:49:52</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-08-27 19:39:28</t>
+          <t>2026-08-27 22:49:52</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-08-27 19:39:28</t>
+          <t>2026-08-27 22:49:52</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-08-27 19:39:28</t>
+          <t>2026-08-27 22:49:52</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-08-27 19:39:29</t>
+          <t>2026-08-27 22:49:53</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3297,7 +3297,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-08-27 19:39:29</t>
+          <t>2026-08-27 22:49:53</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3358,7 +3358,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-08-27 19:39:29</t>
+          <t>2026-08-27 22:49:53</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3419,7 +3419,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-08-27 19:39:29</t>
+          <t>2026-08-27 22:49:53</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-08-27 19:39:29</t>
+          <t>2026-08-27 22:49:53</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
